--- a/backend/excel-templates/defense-showcase/05_master_external_examiners.xlsx
+++ b/backend/excel-templates/defense-showcase/05_master_external_examiners.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Examiners" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -398,56 +398,63 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>firstName</v>
+      </c>
+      <c r="B1" t="str">
+        <v>lastName</v>
+      </c>
+      <c r="C1" t="str">
+        <v>designation</v>
+      </c>
+      <c r="D1" t="str">
         <v>email</v>
       </c>
-      <c r="B1" t="str">
+      <c r="E1" t="str">
         <v>password</v>
-      </c>
-      <c r="C1" t="str">
-        <v>firstName</v>
-      </c>
-      <c r="D1" t="str">
-        <v>lastName</v>
-      </c>
-      <c r="E1" t="str">
-        <v>designation</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>Shashidhar Ram</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Joshi</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Prof. Dr.</v>
+      </c>
+      <c r="D2" t="str">
         <v>shashidhar.joshi@ioe.edu.np</v>
       </c>
-      <c r="B2" t="str">
+      <c r="E2" t="str">
         <v>Test@123Password</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Shashidhar Ram</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Joshi</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Prof. Dr.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>Sanjeeb Prasad</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Panday</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Assoc. Prof. Dr.</v>
+      </c>
+      <c r="D3" t="str">
         <v>sanjeeb.panday@ioe.edu.np</v>
       </c>
-      <c r="B3" t="str">
+      <c r="E3" t="str">
         <v>Test@123Password</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Sanjeeb Prasad</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Panday</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Assoc. Prof. Dr.</v>
       </c>
     </row>
   </sheetData>
